--- a/cds/mm_china-5year-cds.xlsx
+++ b/cds/mm_china-5year-cds.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="657">
   <si>
     <t>Date</t>
   </si>
@@ -1971,6 +1971,21 @@
   </si>
   <si>
     <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
   </si>
 </sst>
 </file>
@@ -2320,7 +2335,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B651"/>
+  <dimension ref="A1:B656"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7529,6 +7544,46 @@
       </c>
       <c r="B651" s="3">
         <v>45.2124</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="B652" s="3">
+        <v>48.3917</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="B653" s="3">
+        <v>49.5049</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="B654" s="3">
+        <v>53.782</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="B655" s="3">
+        <v>52.5517</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="B656" s="3">
+        <v>45.5151</v>
       </c>
     </row>
   </sheetData>
